--- a/templates/test_files/Strukturvorlage_DataDictionary_v5_AreaMgmt.xlsx
+++ b/templates/test_files/Strukturvorlage_DataDictionary_v5_AreaMgmt.xlsx
@@ -12232,7 +12232,7 @@
       </c>
       <c r="AD1" s="188" t="inlineStr">
         <is>
-          <t>Klassifikationen</t>
+          <t>RelatedDocuments</t>
         </is>
       </c>
       <c r="AE1" s="100" t="inlineStr">
